--- a/GeoMIP/results/resultados_Geometric.xlsx
+++ b/GeoMIP/results/resultados_Geometric.xlsx
@@ -464,18 +464,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  b,c,d,e,f,g,h,i,j,k,l,m,n,o  || a |</t>
+          <t>| O || F,G,H,I,J,K,A,B,C,D,L,E,N,M |
+| o || f,g,h,i,j,k,a,b,c,d,l,e,n,m |</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027099132537841797</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4,579893350601196</t>
+          <t>6,044453144073486</t>
         </is>
       </c>
     </row>
@@ -495,18 +495,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  b,c,d,e,f,g,h,i,j,k,l,m,n,o  || a |</t>
+          <t>| O || A,B,D,G,H,I,K,C,J,F,L,E,N,M |
+| o || a,b,d,g,h,i,k,c,j,f,l,e,n,m |</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027099132537841797</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>6,919468402862549</t>
+          <t>5,227648973464966</t>
         </is>
       </c>
     </row>
@@ -524,22 +524,9 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|   c,d,e,f,g,h,i,j,k,l,m,n,o   || b |</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2,118175506591797</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -555,22 +542,9 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|   c,d,e,f,g,h,i,j,k,l,m,n,o   || b |</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2,2138495445251465</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -586,22 +560,9 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,M,N,O || L |
-|       a,c,e,g,i,k,m,o       || ∅ |</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0,0041897893</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0,053345680236816406</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -617,22 +578,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,H,I,J,K,L,M,N,O || G |
-|        b,d,f,h,j,l,n        || ∅ |</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0,03946566581726074</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -648,22 +596,9 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N || O |
-|     a,b,d,e,g,h,j,k,m,n     || ∅ |</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>4,7147274e-05</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0,13345050811767578</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -681,18 +616,18 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  b,c,d,e,f,g,h,i,j,k,l,m,n,o  || a |</t>
+          <t>| O || A,C,D,E,G,J,K,M,N,F,B,L,I,H |
+| o || a,c,d,e,g,j,k,m,n,f,b,l,i,h |</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027099132537841797</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4,621979475021362</t>
+          <t>6,045221328735352</t>
         </is>
       </c>
     </row>
@@ -712,18 +647,18 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  b,c,d,e,f,g,h,i,j,k,l,m,n,o  || a |</t>
+          <t>| J || A,H,I,K,L,M,N,O,B,C,D,F,G,E |
+| j || a,h,i,k,l,m,n,o,b,c,d,f,g,e |</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02764260768890381</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4,582592248916626</t>
+          <t>5,012800455093384</t>
         </is>
       </c>
     </row>
@@ -741,22 +676,9 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|   c,d,e,f,g,h,i,j,k,l,m,n,o   || b |</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2,1731057167053223</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -772,22 +694,9 @@
           <t>011111111111111</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|   c,d,e,f,g,h,i,j,k,l,m,n,o   || b |</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2,102712631225586</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -803,22 +712,9 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,M,N,O || L |
-|       a,c,e,g,i,k,m,o       || ∅ |</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0,0041897893</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0,05184602737426758</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -834,22 +730,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,H,I,J,K,L,M,N,O || G |
-|        b,d,f,h,j,l,n        || ∅ |</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0,03757977485656738</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -865,22 +748,9 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>| A,B,C,D,E,F,G,H,I,J,K,L,M,N || O |
-|     a,b,d,e,g,h,j,k,m,n     || ∅ |</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4,7147274e-05</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0,12448477745056152</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -898,18 +768,18 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| M || B,D,F,H,I,L,N,J,A,E,G,C,K |
+| m || b,d,f,h,i,l,n,j,a,e,g,c,k |</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027572154998779297</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4,861511707305908</t>
+          <t>6,353318452835083</t>
         </is>
       </c>
     </row>
@@ -929,18 +799,18 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| D,F,H,J,K,L,M,C,E,I,N,B,G || A |
+| d,f,h,j,k,l,m,c,e,i,n,b,g || a |</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02756434679031372</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5,02129864692688</t>
+          <t>6,526005983352661</t>
         </is>
       </c>
     </row>
@@ -960,18 +830,18 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  c,d,e,f,g,h,i,j,k,l,m,n,o  || b |</t>
+          <t>| M || B,C,E,F,H,I,J,K,L,N,A,D,G |
+| m || b,c,e,f,h,i,j,k,l,n,a,d,g |</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,026668906211853027</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2,220367193222046</t>
+          <t>2,2186245918273926</t>
         </is>
       </c>
     </row>
@@ -991,18 +861,18 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  c,d,e,f,g,h,i,j,k,l,m,n,o  || b |</t>
+          <t>| J || A,C,I,K,L,M,N,D,E,F,B,G,H |
+| j || a,c,i,k,l,m,n,d,e,f,b,g,h |</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027917683124542236</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2,239171266555786</t>
+          <t>2,2202682495117188</t>
         </is>
       </c>
     </row>
@@ -1020,22 +890,9 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,M,N,O || L |
-|      a,c,e,g,i,k,m,o      || ∅ |</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0,0041897893</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0,05197620391845703</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1051,22 +908,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,H,I,J,K,L,M,N,O || G |
-|       b,d,f,h,j,l,n       || ∅ |</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0,04459977149963379</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1082,22 +926,9 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N || O |
-|    a,b,d,e,g,h,j,k,m,n    || ∅ |</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>4,7147274e-05</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0,1284315586090088</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1115,18 +946,18 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| E || A,C,I,J,M,G,H,K,B,F,N,L,D |
+| e || a,c,i,j,m,g,h,k,b,f,n,l,d |</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02709829807281494</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4,305819272994995</t>
+          <t>6,6611645221710205</t>
         </is>
       </c>
     </row>
@@ -1146,18 +977,18 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| M || B,D,F,G,I,L,A,E,H,J,C,K,N |
+| m || b,d,f,g,i,l,a,e,h,j,c,k,n |</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027572154998779297</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4,329853057861328</t>
+          <t>5,068044185638428</t>
         </is>
       </c>
     </row>
@@ -1177,18 +1008,18 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  c,d,e,f,g,h,i,j,k,l,m,n,o  || b |</t>
+          <t>| F || D,E,H,I,M,A,C,G,B,J,K,L,N |
+| f || d,e,h,i,m,a,c,g,b,j,k,l,n |</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,026921391487121582</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2,0419702529907227</t>
+          <t>2,58276629447937</t>
         </is>
       </c>
     </row>
@@ -1208,18 +1039,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  c,d,e,f,g,h,i,j,k,l,m,n,o  || b |</t>
+          <t>| N || A,C,D,E,F,I,J,M,B,G,H,K,L |
+| n || a,c,d,e,f,i,j,m,b,g,h,k,l |</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,027099132537841797</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1,9676649570465088</t>
+          <t>2,3304874897003174</t>
         </is>
       </c>
     </row>
@@ -1237,22 +1068,9 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,M,N,O || L |
-|      a,c,e,g,i,k,m,o      || ∅ |</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0,0041897893</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0,0475153923034668</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1268,22 +1086,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,H,I,J,K,L,M,N,O || G |
-|       b,d,f,h,j,l,n       || ∅ |</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0,03600168228149414</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1299,22 +1104,9 @@
           <t>110110110110110</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>| B,C,D,E,F,G,H,I,J,K,L,M,N || O |
-|    a,b,d,e,g,h,j,k,m,n    || ∅ |</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>4,7147274e-05</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0,1395430564880371</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1332,18 +1124,18 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>|       A,C,E,G,I,K,M,O       || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| D,E,G,H,F || A,B,C |
+| d,e,g,h,f || a,b,c |</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,20127719640731812</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3,517134428024292</t>
+          <t>4,812572479248047</t>
         </is>
       </c>
     </row>
@@ -1363,18 +1155,18 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>|       A,C,E,G,I,K,M,O       || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| B,C,E,G,H || D,F,A |
+| b,c,e,g,h || d,f,a |</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,2004041075706482</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3,465230941772461</t>
+          <t>3,918609619140625</t>
         </is>
       </c>
     </row>
@@ -1394,18 +1186,18 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>|      A,C,E,G,I,K,M,O      || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| G,B,D,F,C,E || A,H |
+| g,b,d,f,c,e || a,h |</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,20180201530456543</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1,5758247375488281</t>
+          <t>2,0697426795959473</t>
         </is>
       </c>
     </row>
@@ -1425,18 +1217,18 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>|      A,C,E,G,I,K,M,O      || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| E,G,F,D,B,C || A,H |
+| e,g,f,d,b,c || a,h |</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,20180201530456543</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1,598731517791748</t>
+          <t>2,0545265674591064</t>
         </is>
       </c>
     </row>
@@ -1456,18 +1248,18 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>|  A,C,G,I,K,M,O  || E |
-| a,c,e,g,i,k,m,o || ∅ |</t>
+          <t>| C,G || A,D,F,B,H,E |
+| c,g || a,d,f,b,h,e |</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0,0043781996</t>
+          <t>0,03032785654067993</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0,027150869369506836</t>
+          <t>0,08418655395507812</t>
         </is>
       </c>
     </row>
@@ -1485,22 +1277,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>| A,C,E,I,K,M,O || G |
-| b,d,f,h,j,l,n || ∅ |</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0,016974449157714844</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1518,18 +1297,18 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>|    A,C,E,G,I,K,M    || O |
-| a,b,d,e,g,h,j,k,m,n || ∅ |</t>
+          <t>| A,F || B,E,C,G,H,D |
+| a,f || b,e,c,g,h,d |</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4,7147274e-05</t>
+          <t>0,04236578941345215</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0,08824753761291504</t>
+          <t>0,24698209762573242</t>
         </is>
       </c>
     </row>
@@ -1549,18 +1328,18 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>|        B,D,F,H,J,L,N        || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| D,E,F,G || B,C,A |
+| d,e,f,g || b,c,a |</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,18093091249465942</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3,263221263885498</t>
+          <t>4,671905755996704</t>
         </is>
       </c>
     </row>
@@ -1580,18 +1359,18 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>|        B,D,F,H,J,L,N        || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| C,E,G || B,D,F,A |
+| c,e,g || b,d,f,a |</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,17958372831344604</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3,186232805252075</t>
+          <t>3,8274853229522705</t>
         </is>
       </c>
     </row>
@@ -1611,18 +1390,18 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>|       B,D,F,H,J,L,N       || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| B,E,F,G,D || A,C |
+| b,e,f,g,d || a,c |</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,17441809177398682</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1,50034761428833</t>
+          <t>2,3339641094207764</t>
         </is>
       </c>
     </row>
@@ -1642,18 +1421,18 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>|       B,D,F,H,J,L,N       || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| B,E,F,G,D || A,C |
+| b,e,f,g,d || a,c |</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,17441809177398682</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1,4601209163665771</t>
+          <t>2,0738508701324463</t>
         </is>
       </c>
     </row>
@@ -1673,18 +1452,18 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>|   B,D,F,H,J,N   || L |
-| a,c,e,g,i,k,m,o || ∅ |</t>
+          <t>| E || A,B,C,D,F,G |
+| e || a,b,c,d,f,g |</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0,0041897893</t>
+          <t>0,033656179904937744</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0,028932571411132812</t>
+          <t>0,07458615303039551</t>
         </is>
       </c>
     </row>
@@ -1704,18 +1483,18 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>|  B,D,F,H,J,L  || N |
-| b,d,f,h,j,l,n || ∅ |</t>
+          <t>| B || A,G,C,E,D,F |
+| b || a,g,c,e,d,f |</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0,008794069</t>
+          <t>0,021556615829467773</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0,016787290573120117</t>
+          <t>0,06656551361083984</t>
         </is>
       </c>
     </row>
@@ -1735,18 +1514,18 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>|     B,D,F,H,J,L     || N |
-| a,b,d,e,g,h,j,k,m,n || ∅ |</t>
+          <t>| G,B,C,E || D,F,A |
+| g,b,c,e || d,f,a |</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0,0013378263</t>
+          <t>0,0432358980178833</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0,0856177806854248</t>
+          <t>0,15642976760864258</t>
         </is>
       </c>
     </row>
@@ -1766,18 +1545,18 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>|     A,B,D,E,G,H,J,K,M,N     || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| B,C,D,F,H,I,J || A,E,G |
+| b,c,d,f,h,i,j || a,e,g |</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,22736209630966187</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3,900536298751831</t>
+          <t>4,548474550247192</t>
         </is>
       </c>
     </row>
@@ -1797,18 +1576,18 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>|     A,B,D,E,G,H,J,K,M,N     || ∅ |
-| b,c,d,e,f,g,h,i,j,k,l,m,n,o || a |</t>
+          <t>| I || A,C,D,E,G,H,J,B,F |
+| i || a,c,d,e,g,h,j,b,f |</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,21319663524627686</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>3,845041275024414</t>
+          <t>4,58513069152832</t>
         </is>
       </c>
     </row>
@@ -1828,18 +1607,18 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>|    A,B,D,E,G,H,J,K,M,N    || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| B,D,F,H,J,E,G || C,I,A |
+| b,d,f,h,j,e,g || c,i,a |</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,22349542379379272</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1,7483837604522705</t>
+          <t>2,3245882987976074</t>
         </is>
       </c>
     </row>
@@ -1859,18 +1638,18 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>|    A,B,D,E,G,H,J,K,M,N    || ∅ |
-| c,d,e,f,g,h,i,j,k,l,m,n,o || b |</t>
+          <t>| A,B,C,F,G,I,J,H || D,E |
+| a,b,c,f,g,i,j,h || d,e |</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,18966341018676758</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1,7399888038635254</t>
+          <t>1,9799222946166992</t>
         </is>
       </c>
     </row>
@@ -1888,22 +1667,9 @@
           <t>101010101010101</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>| A,B,D,G,H,J,K,M,N || E |
-|  a,c,e,g,i,k,m,o  || ∅ |</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>0,0043781996</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>0,0348660945892334</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1919,22 +1685,9 @@
           <t>010101010101010</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>| A,B,D,E,H,J,K,M,N || G |
-|   b,d,f,h,j,l,n   || ∅ |</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0,0070973635</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>0,022195100784301758</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1952,18 +1705,18 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>|  A,B,D,E,G,H,J,K,M  || N |
-| a,b,d,e,g,h,j,k,m,n || ∅ |</t>
+          <t>| B,C || D,E,F,G,I,J,A,H |
+| b,c || d,e,f,g,i,j,a,h |</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0,0013378263</t>
+          <t>0,03184330463409424</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0,09588932991027832</t>
+          <t>0,28328561782836914</t>
         </is>
       </c>
     </row>
@@ -1983,18 +1736,18 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>| A,C,D,E,F,G,H,I,J,K,L,M,N,O || ∅ |
-|  c,d,e,f,g,h,i,j,k,l,m,n,o  || a |</t>
+          <t>| I || A,C,G,K,L,M,N,D,E,F,H,J,B |
+| i || a,c,g,k,l,m,n,d,e,f,h,j,b |</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02764260768890381</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1,9749562740325928</t>
+          <t>3,4070558547973633</t>
         </is>
       </c>
     </row>
